--- a/Return Authorization Request Spreadsheet Template.xlsx
+++ b/Return Authorization Request Spreadsheet Template.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smithandnephew-my.sharepoint.com/personal/ryan_morris_smith-nephew_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{C837B6CA-0566-4647-BF42-0382BA28F449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83ED8DFE-DAAA-4444-8A60-390AD0DD56CD}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{C837B6CA-0566-4647-BF42-0382BA28F449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DC125BD-2E2F-4A4A-8C57-F14B682782D1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{87E91D51-3528-4A12-B5AE-20859D5A0EA4}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87E91D51-3528-4A12-B5AE-20859D5A0EA4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Information" sheetId="3" r:id="rId1"/>
-    <sheet name="Serial Numbers" sheetId="1" r:id="rId2"/>
+    <sheet name="Serial Numbers" sheetId="1" r:id="rId1"/>
+    <sheet name="Information" sheetId="3" state="hidden" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Serial Numbers'!$A$1:$D$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>Device Type</t>
   </si>
@@ -60,9 +63,6 @@
     <t>RENASYS TOUCH</t>
   </si>
   <si>
-    <t>RENASYS GO</t>
-  </si>
-  <si>
     <t>RENASYS EDGE</t>
   </si>
   <si>
@@ -166,12 +166,6 @@
   </si>
   <si>
     <t>IF DEVICE HAS ERROR, PLEASE PUT ERROR CODE OR MESSAGE IN "ADDITIONAL INFORMATION"</t>
-  </si>
-  <si>
-    <t>VERSAJET</t>
-  </si>
-  <si>
-    <t>CENTRIO</t>
   </si>
   <si>
     <t>Device is at the end of its' Service Life and needs to be disposed of properly</t>
@@ -184,7 +178,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -219,13 +213,6 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -247,15 +234,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -271,10 +257,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -593,206 +575,255 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52DE6BE-D90B-4BD7-9410-783888DD86FD}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Device Type" xr:uid="{F3F53D49-033F-4323-BA43-D0C619635403}">
+          <x14:formula1>
+            <xm:f>Information!$B$3:$B$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>A1:A1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{15D015A9-DA5A-4EE8-8B4D-1ACFD5A53B51}">
+          <x14:formula1>
+            <xm:f>Information!$B$9:$B$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>C1:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD62B7A-A322-4F4F-AC9A-B08DAEC72DA6}">
   <dimension ref="B1:D27"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="72.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.2">
       <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D2" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="D3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="2"/>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" s="2"/>
+      <c r="D7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
         <v>12</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
         <v>13</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
         <v>14</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
         <v>15</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
         <v>16</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -803,32 +834,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52DE6BE-D90B-4BD7-9410-783888DD86FD}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.61328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.765625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{273106dc-2878-42eb-b7c8-069dcf334687}" enabled="0" method="" siteId="{273106dc-2878-42eb-b7c8-069dcf334687}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/Return Authorization Request Spreadsheet Template.xlsx
+++ b/Return Authorization Request Spreadsheet Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smithandnephew-my.sharepoint.com/personal/ryan_morris_smith-nephew_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{C837B6CA-0566-4647-BF42-0382BA28F449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DC125BD-2E2F-4A4A-8C57-F14B682782D1}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{C837B6CA-0566-4647-BF42-0382BA28F449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FEC7918-A8DB-414A-B3D3-8B1A1AF92A03}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87E91D51-3528-4A12-B5AE-20859D5A0EA4}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
   <si>
     <t>Device Type</t>
   </si>
@@ -576,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52DE6BE-D90B-4BD7-9410-783888DD86FD}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -597,14 +597,6 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Return Authorization Request Spreadsheet Template.xlsx
+++ b/Return Authorization Request Spreadsheet Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smithandnephew-my.sharepoint.com/personal/ryan_morris_smith-nephew_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{C837B6CA-0566-4647-BF42-0382BA28F449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FEC7918-A8DB-414A-B3D3-8B1A1AF92A03}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{30FD98F8-A908-4AFD-A415-5C79C9D68F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9913246-2EAD-4AB8-AD4B-594190F53555}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87E91D51-3528-4A12-B5AE-20859D5A0EA4}"/>
+    <workbookView xWindow="19090" yWindow="-10920" windowWidth="38620" windowHeight="21100" xr2:uid="{87E91D51-3528-4A12-B5AE-20859D5A0EA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Serial Numbers" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
   <si>
     <t>Device Type</t>
   </si>
@@ -172,6 +172,30 @@
   </si>
   <si>
     <t>Additional Information (Continued)</t>
+  </si>
+  <si>
+    <t>Error Light- Battery Alarm</t>
+  </si>
+  <si>
+    <t>Error Light- High Vacuum Alarm</t>
+  </si>
+  <si>
+    <t>Error Light- Leak Alarm</t>
+  </si>
+  <si>
+    <t>Error Light- Low Vacuum Alarm</t>
+  </si>
+  <si>
+    <t>Error Light- Canister Full/ Blockage Alarm</t>
+  </si>
+  <si>
+    <t>Error Light- Device failed self-test (EDGE)</t>
+  </si>
+  <si>
+    <t>Investigation Reason</t>
+  </si>
+  <si>
+    <t>No Investigation Necessary</t>
   </si>
 </sst>
 </file>
@@ -234,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -242,6 +266,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,16 +601,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52DE6BE-D90B-4BD7-9410-783888DD86FD}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="77.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,6 +622,9 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -603,7 +632,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Device Type" xr:uid="{F3F53D49-033F-4323-BA43-D0C619635403}">
           <x14:formula1>
             <xm:f>Information!$B$3:$B$4</xm:f>
@@ -616,6 +645,12 @@
           </x14:formula1>
           <xm:sqref>C1:C1048576</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8876A6AF-18C2-456F-B523-ADE0B449D6ED}">
+          <x14:formula1>
+            <xm:f>Information!$B$15:$B$43</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -624,7 +659,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD62B7A-A322-4F4F-AC9A-B08DAEC72DA6}">
-  <dimension ref="B1:D27"/>
+  <dimension ref="B1:D43"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="72.25" bestFit="1" customWidth="1"/>
@@ -731,98 +766,180 @@
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" t="s">
-        <v>35</v>
-      </c>
+      <c r="B15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" s="4"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>22</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="D24:D26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
